--- a/artfynd/A 18460-2023 artfynd.xlsx
+++ b/artfynd/A 18460-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18460-2023 artfynd.xlsx
+++ b/artfynd/A 18460-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>89603526</v>
       </c>
       <c r="B2" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>450028.9954418801</v>
+        <v>450029</v>
       </c>
       <c r="R2" t="n">
-        <v>7087822.919885547</v>
+        <v>7087823</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89603513</v>
+        <v>110580220</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartrun, Jmt</t>
+          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>450060.2126554123</v>
+        <v>450318</v>
       </c>
       <c r="R3" t="n">
-        <v>7087679.78305334</v>
+        <v>7088150</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,27 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,75 +858,70 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89603521</v>
+        <v>110580228</v>
       </c>
       <c r="B4" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartrun, Jmt</t>
+          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>450028.9954418801</v>
+        <v>450288</v>
       </c>
       <c r="R4" t="n">
-        <v>7087822.919885547</v>
+        <v>7088147</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +945,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,37 +959,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89603523</v>
+        <v>110580308</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,37 +989,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Svartrun, Jmt</t>
+          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>450044.8400147054</v>
+        <v>450262</v>
       </c>
       <c r="R5" t="n">
-        <v>7087931.842652846</v>
+        <v>7088143</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,22 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,37 +1060,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89603525</v>
+        <v>89603510</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>450388.1948410851</v>
+        <v>450438</v>
       </c>
       <c r="R6" t="n">
-        <v>7087847.140456564</v>
+        <v>7087861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1147,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110580228</v>
+        <v>89603531</v>
       </c>
       <c r="B7" t="n">
-        <v>76513</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,40 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>314</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>450287.6033928538</v>
+        <v>450505</v>
       </c>
       <c r="R7" t="n">
-        <v>7088146.756647575</v>
+        <v>7087896</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,22 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,34 +1259,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110580308</v>
+        <v>111936787</v>
       </c>
       <c r="B8" t="n">
-        <v>89401</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,40 +1292,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
+          <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>450262.4304980583</v>
+        <v>449922</v>
       </c>
       <c r="R8" t="n">
-        <v>7088143.635188881</v>
+        <v>7088162</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1449,22 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,34 +1360,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110580220</v>
+        <v>89603538</v>
       </c>
       <c r="B9" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,40 +1389,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>450318.5116387127</v>
+        <v>450333</v>
       </c>
       <c r="R9" t="n">
-        <v>7088150.227421151</v>
+        <v>7087804</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,22 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,34 +1457,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110580497</v>
+        <v>89603536</v>
       </c>
       <c r="B10" t="n">
-        <v>73701</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,22 +1508,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>450284.6803151176</v>
+        <v>450507</v>
       </c>
       <c r="R10" t="n">
-        <v>7088045.998939568</v>
+        <v>7087900</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,22 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,34 +1558,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111936803</v>
+        <v>110580497</v>
       </c>
       <c r="B11" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1740,41 +1591,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1467</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Rörvattnet, Ansättån, Hotagen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449957</v>
+        <v>450285</v>
       </c>
       <c r="R11" t="n">
-        <v>7088104</v>
+        <v>7088046</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,17 +1648,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,72 +1662,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111936851</v>
+        <v>111936784</v>
       </c>
       <c r="B12" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449977</v>
+        <v>450334</v>
       </c>
       <c r="R12" t="n">
-        <v>7087786</v>
+        <v>7088178</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,11 +1752,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,54 +1778,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111936821</v>
+        <v>89603525</v>
       </c>
       <c r="B13" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>450360</v>
+        <v>450388</v>
       </c>
       <c r="R13" t="n">
-        <v>7088256</v>
+        <v>7087847</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,17 +1843,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,66 +1863,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111936825</v>
+        <v>89603521</v>
       </c>
       <c r="B14" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6439</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>450327</v>
+        <v>450029</v>
       </c>
       <c r="R14" t="n">
-        <v>7088177</v>
+        <v>7087823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,17 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,27 +1964,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111936891</v>
+        <v>89603513</v>
       </c>
       <c r="B15" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,34 +1991,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>rörvattsbodarna, Jmt</t>
+          <t>Svartrun, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>450088</v>
+        <v>450060</v>
       </c>
       <c r="R15" t="n">
-        <v>7087844</v>
+        <v>7087680</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,12 +2045,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,27 +2070,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111936842</v>
+        <v>111936803</v>
       </c>
       <c r="B16" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,10 +2125,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>450087</v>
+        <v>449957</v>
       </c>
       <c r="R16" t="n">
-        <v>7087895</v>
+        <v>7088104</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2165,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,15 +2192,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111936836</v>
+        <v>111936804</v>
       </c>
       <c r="B17" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2223,11 @@
       <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2425,10 +2235,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>450058</v>
+        <v>449911</v>
       </c>
       <c r="R17" t="n">
-        <v>7087628</v>
+        <v>7088174</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2465,14 +2275,14 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="b">
         <v>0</v>
@@ -2492,15 +2302,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111936834</v>
+        <v>111936805</v>
       </c>
       <c r="B18" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,10 +2341,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>450266</v>
+        <v>449946</v>
       </c>
       <c r="R18" t="n">
-        <v>7087812</v>
+        <v>7088178</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,15 +2408,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111936840</v>
+        <v>111936806</v>
       </c>
       <c r="B19" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>450108</v>
+        <v>449926</v>
       </c>
       <c r="R19" t="n">
-        <v>7087831</v>
+        <v>7088162</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2687,7 +2487,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,15 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111936835</v>
+        <v>111936807</v>
       </c>
       <c r="B20" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2758,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>450185</v>
+        <v>450003</v>
       </c>
       <c r="R20" t="n">
-        <v>7087745</v>
+        <v>7088105</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2798,7 +2593,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2825,15 +2620,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111936815</v>
+        <v>111936809</v>
       </c>
       <c r="B21" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2869,10 +2659,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>450254</v>
+        <v>450019</v>
       </c>
       <c r="R21" t="n">
-        <v>7088083</v>
+        <v>7088106</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,7 +2699,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2936,15 +2726,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111936807</v>
+        <v>111936810</v>
       </c>
       <c r="B22" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,10 +2765,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>450003</v>
+        <v>450076</v>
       </c>
       <c r="R22" t="n">
-        <v>7088105</v>
+        <v>7088074</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3020,7 +2805,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,15 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111936887</v>
+        <v>111936811</v>
       </c>
       <c r="B23" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3063,34 +2843,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>450114</v>
+        <v>450080</v>
       </c>
       <c r="R23" t="n">
-        <v>7087631</v>
+        <v>7088091</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3123,6 +2907,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,15 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111936846</v>
+        <v>111936813</v>
       </c>
       <c r="B24" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3193,10 +2977,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449994</v>
+        <v>450092</v>
       </c>
       <c r="R24" t="n">
-        <v>7087723</v>
+        <v>7088085</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3233,7 +3017,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,15 +3044,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111936883</v>
+        <v>111936814</v>
       </c>
       <c r="B25" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3276,34 +3055,38 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>450282</v>
+        <v>450114</v>
       </c>
       <c r="R25" t="n">
-        <v>7088113</v>
+        <v>7088076</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,6 +3119,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,15 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111936882</v>
+        <v>111936815</v>
       </c>
       <c r="B26" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3378,34 +3161,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>450302</v>
+        <v>450254</v>
       </c>
       <c r="R26" t="n">
-        <v>7088262</v>
+        <v>7088082</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3438,6 +3225,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3464,15 +3256,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111936806</v>
+        <v>111936816</v>
       </c>
       <c r="B27" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,10 +3295,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449926</v>
+        <v>450284</v>
       </c>
       <c r="R27" t="n">
-        <v>7088162</v>
+        <v>7088186</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3575,15 +3362,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>111936824</v>
+        <v>111936817</v>
       </c>
       <c r="B28" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3619,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>450382</v>
+        <v>450279</v>
       </c>
       <c r="R28" t="n">
-        <v>7088202</v>
+        <v>7088213</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3659,7 +3441,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,15 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>111936816</v>
+        <v>111936820</v>
       </c>
       <c r="B29" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3730,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>450284</v>
+        <v>450352</v>
       </c>
       <c r="R29" t="n">
-        <v>7088186</v>
+        <v>7088260</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3797,15 +3574,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111936810</v>
+        <v>111936821</v>
       </c>
       <c r="B30" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3841,10 +3613,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>450077</v>
+        <v>450360</v>
       </c>
       <c r="R30" t="n">
-        <v>7088074</v>
+        <v>7088256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3653,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3908,15 +3680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111936820</v>
+        <v>111936824</v>
       </c>
       <c r="B31" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3952,10 +3719,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>450352</v>
+        <v>450382</v>
       </c>
       <c r="R31" t="n">
-        <v>7088261</v>
+        <v>7088202</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4019,15 +3786,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111936814</v>
+        <v>111936825</v>
       </c>
       <c r="B32" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,10 +3825,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>450115</v>
+        <v>450327</v>
       </c>
       <c r="R32" t="n">
-        <v>7088076</v>
+        <v>7088178</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4103,7 +3865,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,15 +3892,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>111936888</v>
+        <v>111936826</v>
       </c>
       <c r="B33" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4146,34 +3903,38 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>450117</v>
+        <v>450286</v>
       </c>
       <c r="R33" t="n">
-        <v>7087724</v>
+        <v>7088075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4206,6 +3967,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,15 +3998,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>111936880</v>
+        <v>111936827</v>
       </c>
       <c r="B34" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4248,34 +4009,38 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>450225</v>
+        <v>450310</v>
       </c>
       <c r="R34" t="n">
-        <v>7088146</v>
+        <v>7088028</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4308,6 +4073,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,15 +4104,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>111936804</v>
+        <v>111936828</v>
       </c>
       <c r="B35" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4370,11 +4135,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4382,10 +4143,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449911</v>
+        <v>450330</v>
       </c>
       <c r="R35" t="n">
-        <v>7088174</v>
+        <v>7088022</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4422,14 +4183,14 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -4449,15 +4210,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>111936845</v>
+        <v>111936829</v>
       </c>
       <c r="B36" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,10 +4249,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449982</v>
+        <v>450355</v>
       </c>
       <c r="R36" t="n">
-        <v>7087774</v>
+        <v>7088015</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4289,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4560,15 +4316,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>111936787</v>
+        <v>111936831</v>
       </c>
       <c r="B37" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4576,34 +4327,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449922</v>
+        <v>450354</v>
       </c>
       <c r="R37" t="n">
-        <v>7088162</v>
+        <v>7088012</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4636,6 +4391,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4665,12 +4425,7 @@
         <v>111936832</v>
       </c>
       <c r="B38" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,15 +4528,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>111936843</v>
+        <v>111936834</v>
       </c>
       <c r="B39" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4817,7 +4567,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>450061</v>
+        <v>450266</v>
       </c>
       <c r="R39" t="n">
         <v>7087811</v>
@@ -4857,7 +4607,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4884,15 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>111936890</v>
+        <v>111936835</v>
       </c>
       <c r="B40" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4900,34 +4645,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>450091</v>
+        <v>450185</v>
       </c>
       <c r="R40" t="n">
-        <v>7087906</v>
+        <v>7087745</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4960,6 +4709,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4986,15 +4740,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>111936881</v>
+        <v>111936836</v>
       </c>
       <c r="B41" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5002,34 +4751,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>450283</v>
+        <v>450058</v>
       </c>
       <c r="R41" t="n">
-        <v>7088220</v>
+        <v>7087628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5062,6 +4815,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5088,15 +4846,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>111936809</v>
+        <v>111936837</v>
       </c>
       <c r="B42" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5132,10 +4885,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>450019</v>
+        <v>450059</v>
       </c>
       <c r="R42" t="n">
-        <v>7088107</v>
+        <v>7087644</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5172,7 +4925,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5199,15 +4952,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>111936848</v>
+        <v>111936838</v>
       </c>
       <c r="B43" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5243,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449911</v>
+        <v>450064</v>
       </c>
       <c r="R43" t="n">
-        <v>7087656</v>
+        <v>7087678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5283,7 +5031,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5310,50 +5058,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>111936784</v>
+        <v>111936839</v>
       </c>
       <c r="B44" t="n">
-        <v>89517</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>450334</v>
+        <v>450131</v>
       </c>
       <c r="R44" t="n">
-        <v>7088179</v>
+        <v>7087763</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5386,6 +5133,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5412,15 +5164,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>111936828</v>
+        <v>111936840</v>
       </c>
       <c r="B45" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5456,10 +5203,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>450330</v>
+        <v>450108</v>
       </c>
       <c r="R45" t="n">
-        <v>7088022</v>
+        <v>7087831</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5523,15 +5270,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>111936889</v>
+        <v>111936842</v>
       </c>
       <c r="B46" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5539,34 +5281,38 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>450085</v>
+        <v>450087</v>
       </c>
       <c r="R46" t="n">
-        <v>7087870</v>
+        <v>7087894</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5599,6 +5345,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,15 +5376,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>111936850</v>
+        <v>111936843</v>
       </c>
       <c r="B47" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5669,10 +5415,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>449960</v>
+        <v>450061</v>
       </c>
       <c r="R47" t="n">
-        <v>7087778</v>
+        <v>7087811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5709,7 +5455,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5736,15 +5482,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>111936829</v>
+        <v>111936844</v>
       </c>
       <c r="B48" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5780,10 +5521,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>450355</v>
+        <v>450042</v>
       </c>
       <c r="R48" t="n">
-        <v>7088015</v>
+        <v>7087785</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5820,7 +5561,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5847,15 +5588,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>111936831</v>
+        <v>111936845</v>
       </c>
       <c r="B49" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5891,10 +5627,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>450354</v>
+        <v>449983</v>
       </c>
       <c r="R49" t="n">
-        <v>7088012</v>
+        <v>7087774</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5931,7 +5667,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5958,15 +5694,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111936817</v>
+        <v>111936846</v>
       </c>
       <c r="B50" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6002,10 +5733,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>450279</v>
+        <v>449994</v>
       </c>
       <c r="R50" t="n">
-        <v>7088213</v>
+        <v>7087723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6042,7 +5773,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6069,15 +5800,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>111936886</v>
+        <v>111936847</v>
       </c>
       <c r="B51" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6085,34 +5811,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>rörvattsbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>450161</v>
+        <v>449952</v>
       </c>
       <c r="R51" t="n">
-        <v>7087694</v>
+        <v>7087533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6145,6 +5875,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6171,15 +5906,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>111936805</v>
+        <v>111936848</v>
       </c>
       <c r="B52" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6215,10 +5945,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>449946</v>
+        <v>449911</v>
       </c>
       <c r="R52" t="n">
-        <v>7088179</v>
+        <v>7087656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6282,15 +6012,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>111936847</v>
+        <v>111936849</v>
       </c>
       <c r="B53" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6326,10 +6051,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>449953</v>
+        <v>449924</v>
       </c>
       <c r="R53" t="n">
-        <v>7087533</v>
+        <v>7087659</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6366,7 +6091,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6393,15 +6118,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111936844</v>
+        <v>111936850</v>
       </c>
       <c r="B54" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,10 +6157,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>450042</v>
+        <v>449959</v>
       </c>
       <c r="R54" t="n">
-        <v>7087785</v>
+        <v>7087778</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6477,7 +6197,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6504,15 +6224,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>111936826</v>
+        <v>111936851</v>
       </c>
       <c r="B55" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6548,10 +6263,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>450286</v>
+        <v>449977</v>
       </c>
       <c r="R55" t="n">
-        <v>7088075</v>
+        <v>7087786</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6588,7 +6303,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6612,987 +6327,6 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>111936884</v>
-      </c>
-      <c r="B56" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>450409</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7087882</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>111936813</v>
-      </c>
-      <c r="B57" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>450091</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7088086</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>111936811</v>
-      </c>
-      <c r="B58" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>450080</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7088091</v>
-      </c>
-      <c r="S58" t="n">
-        <v>10</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>111936839</v>
-      </c>
-      <c r="B59" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>450132</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7087763</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>111936849</v>
-      </c>
-      <c r="B60" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>449924</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7087660</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>111936837</v>
-      </c>
-      <c r="B61" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>450059</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7087644</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>111936885</v>
-      </c>
-      <c r="B62" t="n">
-        <v>89571</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>450183</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7087782</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>111936827</v>
-      </c>
-      <c r="B63" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>450310</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7088028</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>111936838</v>
-      </c>
-      <c r="B64" t="n">
-        <v>56430</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>rörvattsbodarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>450065</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7087678</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Hotagen</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2023-09-05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18460-2023 artfynd.xlsx
+++ b/artfynd/A 18460-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603526</t>
         </is>
       </c>
     </row>
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110580220</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110580228</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110580308</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603510</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603531</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936787</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603538</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603536</t>
         </is>
       </c>
     </row>
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110580497</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936784</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603525</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603521</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2081,6 +2151,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89603513</t>
         </is>
       </c>
     </row>
@@ -2189,6 +2264,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936803</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936804</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936805</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936806</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2617,6 +2712,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936807</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2723,6 +2823,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936809</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2829,6 +2934,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936810</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2935,6 +3045,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936811</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936813</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3147,6 +3267,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936814</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936815</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3359,6 +3489,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936816</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3465,6 +3600,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936817</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3571,6 +3711,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936820</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3677,6 +3822,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936821</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3783,6 +3933,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936824</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3889,6 +4044,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936825</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3995,6 +4155,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936826</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4101,6 +4266,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936827</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4207,6 +4377,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936828</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4313,6 +4488,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936829</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4419,6 +4599,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936831</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4525,6 +4710,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936832</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4631,6 +4821,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936834</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4737,6 +4932,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936835</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4843,6 +5043,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936836</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4949,6 +5154,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936837</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5055,6 +5265,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936838</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5161,6 +5376,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936839</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5267,6 +5487,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936840</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5373,6 +5598,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936842</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5479,6 +5709,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936843</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5585,6 +5820,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936844</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5691,6 +5931,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936845</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5797,6 +6042,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936846</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5903,6 +6153,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936847</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6009,6 +6264,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936848</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6115,6 +6375,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936849</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6221,6 +6486,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936850</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6327,8 +6597,69 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111936851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>